--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826627</v>
+        <v>122826774</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,19 +709,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581070</v>
+        <v>581049</v>
       </c>
       <c r="R2" t="n">
-        <v>6383192</v>
+        <v>6383204</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,19 +753,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -911,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826774</v>
+        <v>122826681</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>97309</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,43 +918,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R4" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -989,9 +979,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826681</v>
+        <v>122826627</v>
       </c>
       <c r="B5" t="n">
-        <v>97301</v>
+        <v>57848</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581058</v>
+        <v>581070</v>
       </c>
       <c r="R5" t="n">
-        <v>6383202</v>
+        <v>6383192</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827129</v>
+        <v>122826681</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>97309</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,53 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R3" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826681</v>
+        <v>122827129</v>
       </c>
       <c r="B4" t="n">
-        <v>97309</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,41 +906,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R4" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826774</v>
+        <v>122827129</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
@@ -726,7 +733,7 @@
         <v>6383204</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,9 +760,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826681</v>
+        <v>122826774</v>
       </c>
       <c r="B3" t="n">
-        <v>97309</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +811,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R3" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -855,19 +877,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827129</v>
+        <v>122826681</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>97311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,53 +918,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R4" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122827129</v>
+        <v>122826774</v>
       </c>
       <c r="B2" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
@@ -733,7 +726,7 @@
         <v>6383204</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -760,19 +753,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826774</v>
+        <v>122826681</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>97311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R3" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -877,9 +855,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826681</v>
+        <v>122827129</v>
       </c>
       <c r="B4" t="n">
-        <v>97311</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,41 +906,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R4" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826681</v>
+        <v>122827129</v>
       </c>
       <c r="B3" t="n">
-        <v>97311</v>
+        <v>57631</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +794,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R3" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827129</v>
+        <v>122826627</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,50 +918,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581049</v>
+        <v>581070</v>
       </c>
       <c r="R4" t="n">
-        <v>6383204</v>
+        <v>6383192</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826627</v>
+        <v>122826681</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>97319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581070</v>
+        <v>581058</v>
       </c>
       <c r="R5" t="n">
-        <v>6383192</v>
+        <v>6383202</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826774</v>
+        <v>122826681</v>
       </c>
       <c r="B2" t="n">
-        <v>57494</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R2" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,9 +748,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827129</v>
+        <v>122826627</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,50 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581049</v>
+        <v>581070</v>
       </c>
       <c r="R3" t="n">
-        <v>6383204</v>
+        <v>6383192</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -869,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826627</v>
+        <v>122826774</v>
       </c>
       <c r="B4" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,20 +911,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,19 +933,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581070</v>
+        <v>581049</v>
       </c>
       <c r="R4" t="n">
-        <v>6383192</v>
+        <v>6383204</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,19 +977,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826681</v>
+        <v>122827129</v>
       </c>
       <c r="B5" t="n">
-        <v>97319</v>
+        <v>57631</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,41 +1018,53 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R5" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826681</v>
+        <v>122826627</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
+        <v>57848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581058</v>
+        <v>581070</v>
       </c>
       <c r="R2" t="n">
-        <v>6383202</v>
+        <v>6383192</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826627</v>
+        <v>122826774</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57494</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,19 +821,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581070</v>
+        <v>581049</v>
       </c>
       <c r="R3" t="n">
-        <v>6383192</v>
+        <v>6383204</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +865,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826774</v>
+        <v>122827129</v>
       </c>
       <c r="B4" t="n">
-        <v>57494</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,29 +910,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
@@ -950,7 +952,7 @@
         <v>6383204</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,9 +979,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827129</v>
+        <v>122826681</v>
       </c>
       <c r="B5" t="n">
-        <v>57631</v>
+        <v>97319</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,53 +1030,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R5" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826627</v>
+        <v>122826681</v>
       </c>
       <c r="B2" t="n">
-        <v>57848</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581070</v>
+        <v>581058</v>
       </c>
       <c r="R2" t="n">
-        <v>6383192</v>
+        <v>6383202</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826774</v>
+        <v>122826627</v>
       </c>
       <c r="B3" t="n">
-        <v>57494</v>
+        <v>57848</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,24 +821,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581049</v>
+        <v>581070</v>
       </c>
       <c r="R3" t="n">
-        <v>6383204</v>
+        <v>6383192</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,9 +860,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1018,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826681</v>
+        <v>122826774</v>
       </c>
       <c r="B5" t="n">
-        <v>97319</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,38 +1035,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R5" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1091,19 +1101,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122826681</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826627</v>
+        <v>122826774</v>
       </c>
       <c r="B3" t="n">
-        <v>57848</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,20 +799,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -821,19 +821,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581070</v>
+        <v>581049</v>
       </c>
       <c r="R3" t="n">
-        <v>6383192</v>
+        <v>6383204</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +865,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827129</v>
+        <v>122826627</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>57851</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,50 +906,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581049</v>
+        <v>581070</v>
       </c>
       <c r="R4" t="n">
-        <v>6383204</v>
+        <v>6383192</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826774</v>
+        <v>122827129</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,29 +1022,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
@@ -1074,7 +1064,7 @@
         <v>6383204</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,9 +1091,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826681</v>
+        <v>122826774</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,43 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R2" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -748,19 +753,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826774</v>
+        <v>122826681</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>97324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,43 +794,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R3" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -865,9 +855,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826627</v>
+        <v>122827129</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,38 +906,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581070</v>
+        <v>581049</v>
       </c>
       <c r="R4" t="n">
-        <v>6383192</v>
+        <v>6383204</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -969,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +991,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122827129</v>
+        <v>122826627</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1018,50 +1030,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581049</v>
+        <v>581070</v>
       </c>
       <c r="R5" t="n">
-        <v>6383204</v>
+        <v>6383192</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826774</v>
+        <v>122826681</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
+        <v>97330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R2" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -753,9 +748,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122826681</v>
+        <v>122827129</v>
       </c>
       <c r="B3" t="n">
-        <v>97324</v>
+        <v>57634</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,41 +799,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581058</v>
+        <v>581049</v>
       </c>
       <c r="R3" t="n">
-        <v>6383202</v>
+        <v>6383204</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122827129</v>
+        <v>122826774</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,36 +927,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
@@ -952,7 +962,7 @@
         <v>6383204</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,19 +989,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 3781-2025 artfynd.xlsx
+++ b/artfynd/A 3781-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122826681</v>
+        <v>122826627</v>
       </c>
       <c r="B2" t="n">
-        <v>97330</v>
+        <v>57851</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581058</v>
+        <v>581070</v>
       </c>
       <c r="R2" t="n">
-        <v>6383202</v>
+        <v>6383192</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122827129</v>
+        <v>122826681</v>
       </c>
       <c r="B3" t="n">
-        <v>57634</v>
+        <v>97333</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,53 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581049</v>
+        <v>581058</v>
       </c>
       <c r="R3" t="n">
-        <v>6383204</v>
+        <v>6383202</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122826774</v>
+        <v>122827129</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,29 +915,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
@@ -962,7 +957,7 @@
         <v>6383204</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,9 +984,19 @@
           <t>2025-03-01</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122826627</v>
+        <v>122826774</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,20 +1035,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1052,19 +1057,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Henriksberg, Henriksberg, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581070</v>
+        <v>581049</v>
       </c>
       <c r="R5" t="n">
-        <v>6383192</v>
+        <v>6383204</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,19 +1101,9 @@
           <t>2025-03-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:26</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:26</t>
         </is>
       </c>
       <c r="AD5" t="b">
